--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/RELÉ PARTIDA - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/RELÉ PARTIDA - 29_01.xlsx
@@ -479,12 +479,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,11 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -603,7 +607,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -616,7 +624,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>RELE PARTIDA IRON NXR125 2003 A 2004/ NXR150 ATÉ 2008/ BIZ125/ CG TITAN150 ATÉ 2008 027518</t>
+          <t>RELE PARTIDA IRON NX200 2003 A 2004/ XR200 ATÉ 2008/ CG TITAN150 ATÉ 2008 027518</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -624,7 +632,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -645,7 +657,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -743,7 +759,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>80</t>
         </is>
       </c>
     </row>
@@ -766,7 +782,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -787,7 +807,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -804,7 +828,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -875,7 +903,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -918,12 +950,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -996,7 +1028,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1012,7 +1048,11 @@
           <t>RELE PARTIDA IRON PCX150 2014 A 2015 352040</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/RELÉ PARTIDA - 29_01.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/RELÉ PARTIDA - 29_01.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>17</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>8</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -757,11 +692,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -782,11 +712,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -807,11 +732,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -828,11 +748,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -853,11 +768,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -878,11 +788,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -903,11 +808,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -928,11 +828,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -953,11 +848,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -978,11 +868,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1003,11 +888,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1028,11 +908,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1053,7 +928,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1066,7 +940,6 @@
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
